--- a/public/material/material-de-apoio.xlsx
+++ b/public/material/material-de-apoio.xlsx
@@ -3,15 +3,20 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Estou fazendo um site para um m" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Dados" sheetId="1" r:id="rId5"/>
+    <sheet state="hidden" name="Dashboard Acompanhamento 2" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Dashboard Acompanhamento" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
+  <pivotCaches>
+    <pivotCache cacheId="0" r:id="rId8"/>
+  </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="38">
   <si>
     <t>ID</t>
   </si>
@@ -90,12 +95,48 @@
   <si>
     <t>Júlia Pires</t>
   </si>
+  <si>
+    <t>ACOMPANHAMENTO PEDAGÓGICO 2026</t>
+  </si>
+  <si>
+    <t>Quantidade de Alunos</t>
+  </si>
+  <si>
+    <t>ACOMPANHAMENTO NA EAD</t>
+  </si>
+  <si>
+    <t>SUM de Acessos Totais</t>
+  </si>
+  <si>
+    <t>SUM de Nota Média (0-100)</t>
+  </si>
+  <si>
+    <t>Média da Taxa de Entrega</t>
+  </si>
+  <si>
+    <t>Média de Entregas com Atraso</t>
+  </si>
+  <si>
+    <t>Média de entrega</t>
+  </si>
+  <si>
+    <t>Postagem</t>
+  </si>
+  <si>
+    <t>Postagens no Fórum</t>
+  </si>
+  <si>
+    <t>Nota Média</t>
+  </si>
+  <si>
+    <t>Total geral</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -107,13 +148,56 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18.0"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="FF134F5C"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8E7CC3"/>
+        <bgColor rgb="FF8E7CC3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF351C75"/>
+        <bgColor rgb="FF351C75"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0E0E3"/>
+        <bgColor rgb="FFD0E0E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF134F5C"/>
+        <bgColor rgb="FF134F5C"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -122,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -132,6 +216,21 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="9" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -140,12 +239,3693 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Quantidade de Alunos x Risco de Evasão</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Dashboard Acompanhamento 2'!$B$4</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="00FF00"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00FF00"/>
+              </a:solidFill>
+              <a:ln cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFFF00"/>
+              </a:solidFill>
+              <a:ln cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Dashboard Acompanhamento 2'!$A$5:$A$7</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Dashboard Acompanhamento 2'!$B$5:$B$7</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="1495173675"/>
+        <c:axId val="1122870245"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1495173675"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Risco de Evasão</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1122870245"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1122870245"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Quantidade de Alunos</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1495173675"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Dashboard Acompanhamento 2'!$E$4</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Dashboard Acompanhamento 2'!$D$5:$D$7</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Dashboard Acompanhamento 2'!$E$5:$E$7</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="880355645"/>
+        <c:axId val="19062152"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="880355645"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="19062152"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="19062152"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="880355645"/>
+      </c:valAx>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Dashboard Acompanhamento 2'!$F$4</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Dashboard Acompanhamento 2'!$D$5:$D$7</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Dashboard Acompanhamento 2'!$F$5:$F$7</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="932384404"/>
+        <c:axId val="156138299"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="932384404"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="156138299"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="156138299"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="932384404"/>
+        <c:crosses val="max"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Alunos x Postagens no Fórum</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Dashboard Acompanhamento 2'!$I$4</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Dashboard Acompanhamento 2'!$H$5:$H$14</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Dashboard Acompanhamento 2'!$I$5:$I$14</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="1274503159"/>
+        <c:axId val="374649336"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1274503159"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Nome do Aluno</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="374649336"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="374649336"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Postagem</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1274503159"/>
+        <c:crosses val="max"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Nota Média e Acessos Totais</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Dashboard Acompanhamento 2'!$M$4</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln cmpd="sng">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Dashboard Acompanhamento 2'!$L$5:$L$14</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Dashboard Acompanhamento 2'!$M$5:$M$14</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1883582449"/>
+        <c:axId val="1368710849"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1883582449"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Nota Média</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1368710849"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1368710849"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Acessos Totais</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1883582449"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Quantidade de Alunos x Risco de Evasão</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Dashboard Acompanhamento'!$B$4</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00FF00"/>
+              </a:solidFill>
+              <a:ln cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFFF00"/>
+              </a:solidFill>
+              <a:ln cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Dashboard Acompanhamento'!$A$5:$A$8</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Dashboard Acompanhamento'!$B$5:$B$8</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="244059672"/>
+        <c:axId val="1704792247"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="244059672"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Risco de Evasão</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1704792247"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1704792247"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="244059672"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Acessos Totais x Notas Médias</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln cmpd="sng">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+          </c:dPt>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Dashboard Acompanhamento'!$F$4:$F$14</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Dashboard Acompanhamento'!$E$4:$E$14</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="220434140"/>
+        <c:axId val="466212435"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="220434140"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Nota Média</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="466212435"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="466212435"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Acessos Totais</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="220434140"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Alunos x Postagens no Fórum</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Dashboard Acompanhamento'!$B$10</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Dashboard Acompanhamento'!$A$11:$A$20</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Dashboard Acompanhamento'!$B$11:$B$20</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="1495391396"/>
+        <c:axId val="2045025740"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1495391396"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Nome do Aluno</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2045025740"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2045025740"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Soma de Postagens no Fórum</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1495391396"/>
+        <c:crosses val="max"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Dashboard Acompanhamento'!$I$4</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Dashboard Acompanhamento'!$H$5:$H$7</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Dashboard Acompanhamento'!$I$5:$I$7</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="267639988"/>
+        <c:axId val="1755352701"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="267639988"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1755352701"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1755352701"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="267639988"/>
+      </c:valAx>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Dashboard Acompanhamento'!$J$4</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Dashboard Acompanhamento'!$H$5:$H$7</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Dashboard Acompanhamento'!$J$5:$J$7</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="1962568220"/>
+        <c:axId val="560495383"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1962568220"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="560495383"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="560495383"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1962568220"/>
+        <c:crosses val="max"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="7038975" cy="3533775"/>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 2" title="Gráfico"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="7038975" cy="3533775"/>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 3" title="Gráfico"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6915150" cy="3533775"/>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 4" title="Gráfico"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6981825" cy="3533775"/>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 8" title="Gráfico"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="7077075" cy="3533775"/>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1" name="Chart 1" title="Gráfico"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="7077075" cy="3533775"/>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 5" title="Gráfico"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="7077075" cy="3533775"/>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 6" title="Gráfico"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="7077075" cy="3533775"/>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 7" title="Gráfico"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" invalid="1" refreshOnLoad="1">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:J11" sheet="Dados"/>
+  </cacheSource>
+  <cacheFields>
+    <cacheField name="ID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1">
+        <n v="1.0"/>
+        <n v="2.0"/>
+        <n v="3.0"/>
+        <n v="4.0"/>
+        <n v="5.0"/>
+        <n v="6.0"/>
+        <n v="7.0"/>
+        <n v="8.0"/>
+        <n v="9.0"/>
+        <n v="10.0"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Nome do Aluno" numFmtId="0">
+      <sharedItems>
+        <s v="Ana Souza"/>
+        <s v="Bruno Lima"/>
+        <s v="Carlos Mendes"/>
+        <s v="Daniela Costa"/>
+        <s v="Eduardo Silva"/>
+        <s v="Fernanda Rocha"/>
+        <s v="Gustavo Alves"/>
+        <s v="Helena Nunes"/>
+        <s v="Igor Martins"/>
+        <s v="Júlia Pires"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Polo/Turma" numFmtId="0">
+      <sharedItems>
+        <s v="Turma A"/>
+        <s v="Turma B"/>
+        <s v="Turma C"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Último Acesso (Dias)" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1">
+        <n v="1.0"/>
+        <n v="14.0"/>
+        <n v="2.0"/>
+        <n v="7.0"/>
+        <n v="0.0"/>
+        <n v="21.0"/>
+        <n v="3.0"/>
+        <n v="10.0"/>
+        <n v="4.0"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Acessos Totais" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1">
+        <n v="145.0"/>
+        <n v="32.0"/>
+        <n v="110.0"/>
+        <n v="54.0"/>
+        <n v="210.0"/>
+        <n v="15.0"/>
+        <n v="88.0"/>
+        <n v="134.0"/>
+        <n v="45.0"/>
+        <n v="76.0"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Postagens Fórum" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1">
+        <n v="8.0"/>
+        <n v="1.0"/>
+        <n v="5.0"/>
+        <n v="2.0"/>
+        <n v="12.0"/>
+        <n v="0.0"/>
+        <n v="3.0"/>
+        <n v="6.0"/>
+        <n v="4.0"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Taxa de Entrega (%)" numFmtId="9">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1">
+        <n v="1.0"/>
+        <n v="0.4"/>
+        <n v="0.9"/>
+        <n v="0.6"/>
+        <n v="0.2"/>
+        <n v="0.8"/>
+        <n v="0.5"/>
+        <n v="0.7"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Entregas com Atraso" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1">
+        <n v="0.0"/>
+        <n v="3.0"/>
+        <n v="1.0"/>
+        <n v="4.0"/>
+        <n v="2.0"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Nota Média (0-100)" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1">
+        <n v="92.0"/>
+        <n v="45.0"/>
+        <n v="85.0"/>
+        <n v="65.0"/>
+        <n v="98.0"/>
+        <n v="30.0"/>
+        <n v="72.0"/>
+        <n v="88.0"/>
+        <n v="55.0"/>
+        <n v="68.0"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Risco de Evasão" numFmtId="0">
+      <sharedItems>
+        <s v="Baixo"/>
+        <s v="Alto"/>
+        <s v="Médio"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Dashboard Acompanhamento 2" cacheId="0" dataCaption="" rowGrandTotals="0" compact="0" compactData="0">
+  <location ref="A4:B7" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields>
+    <pivotField name="ID" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Nome do Aluno" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Polo/Turma" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Último Acesso (Dias)" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Acessos Totais" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Postagens Fórum" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Taxa de Entrega (%)" compact="0" numFmtId="9" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Entregas com Atraso" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Nota Média (0-100)" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Risco de Evasão" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields>
+    <field x="9"/>
+  </rowFields>
+  <dataFields>
+    <dataField name="Quantidade de Alunos" fld="1" subtotal="count" baseField="0"/>
+  </dataFields>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Dashboard Acompanhamento 2 2" cacheId="0" dataCaption="" rowGrandTotals="0" compact="0" compactData="0">
+  <location ref="D4:F7" firstHeaderRow="0" firstDataRow="2" firstDataCol="0"/>
+  <pivotFields>
+    <pivotField name="ID" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Nome do Aluno" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Polo/Turma" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Último Acesso (Dias)" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Acessos Totais" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Postagens Fórum" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Taxa de Entrega (%)" dataField="1" compact="0" numFmtId="9" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Entregas com Atraso" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Nota Média (0-100)" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Risco de Evasão" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields>
+    <field x="2"/>
+  </rowFields>
+  <colFields>
+    <field x="-2"/>
+  </colFields>
+  <dataFields>
+    <dataField name="Média de entrega" fld="6" subtotal="average" baseField="0"/>
+    <dataField name="Média de Entregas com Atraso" fld="7" subtotal="average" baseField="0"/>
+  </dataFields>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Dashboard Acompanhamento 2 3" cacheId="0" dataCaption="" compact="0" compactData="0">
+  <location ref="H4:I15" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields>
+    <pivotField name="ID" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Nome do Aluno" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Polo/Turma" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Último Acesso (Dias)" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Acessos Totais" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Postagens Fórum" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Taxa de Entrega (%)" compact="0" numFmtId="9" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Entregas com Atraso" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Nota Média (0-100)" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Risco de Evasão" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields>
+    <field x="1"/>
+  </rowFields>
+  <dataFields>
+    <dataField name="Postagem" fld="5" baseField="0"/>
+  </dataFields>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Dashboard Acompanhamento 2 4" cacheId="0" dataCaption="" compact="0" compactData="0">
+  <location ref="K4:M15" firstHeaderRow="0" firstDataRow="2" firstDataCol="0"/>
+  <pivotFields>
+    <pivotField name="ID" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Nome do Aluno" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Polo/Turma" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Último Acesso (Dias)" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Acessos Totais" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Postagens Fórum" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Taxa de Entrega (%)" compact="0" numFmtId="9" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Entregas com Atraso" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Nota Média (0-100)" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Risco de Evasão" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields>
+    <field x="1"/>
+  </rowFields>
+  <colFields>
+    <field x="-2"/>
+  </colFields>
+  <dataFields>
+    <dataField name="Nota Média" fld="8" baseField="0"/>
+    <dataField name="Acessos Totais" fld="4" baseField="0"/>
+  </dataFields>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Dashboard Acompanhamento" cacheId="0" dataCaption="" rowGrandTotals="0" compact="0" compactData="0">
+  <location ref="A4:B7" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields>
+    <pivotField name="ID" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Nome do Aluno" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Polo/Turma" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Último Acesso (Dias)" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Acessos Totais" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Postagens Fórum" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Taxa de Entrega (%)" compact="0" numFmtId="9" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Entregas com Atraso" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Nota Média (0-100)" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Risco de Evasão" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields>
+    <field x="9"/>
+  </rowFields>
+  <dataFields>
+    <dataField name="Quantidade de Alunos" fld="1" subtotal="count" baseField="0"/>
+  </dataFields>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Dashboard Acompanhamento 2" cacheId="0" dataCaption="" rowGrandTotals="0" compact="0" compactData="0">
+  <location ref="D4:F14" firstHeaderRow="0" firstDataRow="2" firstDataCol="0"/>
+  <pivotFields>
+    <pivotField name="ID" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Nome do Aluno" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Polo/Turma" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Último Acesso (Dias)" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Acessos Totais" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Postagens Fórum" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Taxa de Entrega (%)" compact="0" numFmtId="9" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Entregas com Atraso" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Nota Média (0-100)" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Risco de Evasão" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields>
+    <field x="1"/>
+  </rowFields>
+  <colFields>
+    <field x="-2"/>
+  </colFields>
+  <dataFields>
+    <dataField name="SUM of Acessos Totais" fld="4" baseField="0"/>
+    <dataField name="SUM of Nota Média (0-100)" fld="8" baseField="0"/>
+  </dataFields>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Dashboard Acompanhamento 3" cacheId="0" dataCaption="" rowGrandTotals="0" compact="0" compactData="0">
+  <location ref="H4:J7" firstHeaderRow="0" firstDataRow="2" firstDataCol="0"/>
+  <pivotFields>
+    <pivotField name="ID" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Nome do Aluno" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Polo/Turma" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Último Acesso (Dias)" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Acessos Totais" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Postagens Fórum" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Taxa de Entrega (%)" dataField="1" compact="0" numFmtId="9" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Entregas com Atraso" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Nota Média (0-100)" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Risco de Evasão" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields>
+    <field x="2"/>
+  </rowFields>
+  <colFields>
+    <field x="-2"/>
+  </colFields>
+  <dataFields>
+    <dataField name="Média da Taxa de Entrega" fld="6" subtotal="average" baseField="0"/>
+    <dataField name="Média de Entregas com Atraso" fld="7" subtotal="average" baseField="0"/>
+  </dataFields>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Dashboard Acompanhamento 4" cacheId="0" dataCaption="" rowGrandTotals="0" compact="0" compactData="0">
+  <location ref="A10:B20" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields>
+    <pivotField name="ID" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Nome do Aluno" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Polo/Turma" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Último Acesso (Dias)" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Acessos Totais" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Postagens Fórum" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Taxa de Entrega (%)" compact="0" numFmtId="9" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Entregas com Atraso" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Nota Média (0-100)" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Risco de Evasão" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields>
+    <field x="1"/>
+  </rowFields>
+  <dataFields>
+    <dataField name="Postagens no Fórum" fld="5" baseField="0"/>
+  </dataFields>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -711,4 +4491,182 @@
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="5" max="5" width="14.0"/>
+    <col customWidth="1" min="6" max="6" width="23.88"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30.0" customHeight="1">
+      <c r="A1" s="8"/>
+      <c r="B1" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="8"/>
+      <c r="X1" s="8"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="8"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="10"/>
+    </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+  </sheetData>
+  <drawing r:id="rId5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="17.5"/>
+    <col customWidth="1" min="5" max="5" width="15.38"/>
+    <col customWidth="1" min="6" max="6" width="21.88"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="39.0" customHeight="1">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
+      <c r="Z1" s="5"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+    </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+  </sheetData>
+  <drawing r:id="rId5"/>
+</worksheet>
 </file>